--- a/tool/release-copy-lucian-freud-tl-26.xlsx
+++ b/tool/release-copy-lucian-freud-tl-26.xlsx
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B47" s="10">
-        <f>IF($B$12="yes",$B$13&amp;" from the "&amp;$B$11&amp;" series",$B$11&amp;", "&amp;$B$13)</f>
+        <f>IF($B$12="yes",$B$13&amp;" from the "&amp;$B$11&amp;" series",IF($B$14=1,$B$11&amp;", "&amp;$B$13,$B$13))</f>
         <v/>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4594,130 +4594,142 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Fragments</t>
+          <t>Naming the work</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Four per release, written once: bio (2 to 3 sentences, Coming Soon only), hook (1 to 2 sentences about the work, in every post and email), making (one sentence on how it was made), quote (verbatim). The hook and bio must not repeat each other.</t>
+          <t>The opener names the work only for a single print: 'The Changeling, a new limited edition print'. A pair or a quartet is just the edition phrase, and the hook names the work; many sets have no collective name anyway. Untitled works from a named series read 'six new limited edition prints from the Dream House series'.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>Fragments</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Fragments are voice-neutral: no we or our, no artist name in the hook or the making line, and 'printmakers at Make-Ready' where it applies. The sheet adds 'our'. The Insiders email and the first-time survey are signed by the advisor named on Inputs. Features never say 'our'.</t>
+          <t>Four per release, written once: bio (2 to 3 sentences, Coming Soon only), hook (1 to 2 sentences about the work, in every post and email), making (one sentence on how it was made), quote (verbatim). The hook and bio must not repeat each other.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Who and what</t>
+          <t>Voice</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>'by {artist}' is always the artist. 'collaboration with {collab_with}' is the artist's name, or the estate. 'unit' is what one is called (print, embroidery, sculpture), and the sheet writes 'a print' or 'an embroidery' wherever a line names one.</t>
+          <t>Fragments are voice-neutral: no we or our, no artist name in the hook or the making line, and 'printmakers at Make-Ready' where it applies. The sheet adds 'our'. The Insiders email and the first-time survey are signed by the advisor named on Inputs. Features never say 'our'.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Who and what</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>The standard three (signed by the artist, individually numbered, free worldwide shipping) plus anything bespoke: framed, a set offer, a partner credit. One line of short sentences in a post, a list in an email. The beneficiary follows, named once.</t>
+          <t>'by {artist}' is always the artist. 'collaboration with {collab_with}' is the artist's name, or the estate. 'unit' is what one is called (print, embroidery, sculpture), and the sheet writes 'a print' or 'an embroidery' wherever a line names one.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Beneficiary</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>One phrase everywhere: 'released in support of'. It goes in the opener unless the hook already names the beneficiary.</t>
+          <t>The standard three (signed by the artist, individually numbered, free worldwide shipping) plus anything bespoke: framed, a set offer, a partner credit. One line of short sentences in a post, a list in an email. The beneficiary follows, named once.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Framing offer</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>A framing code on Inputs adds the first-purchase framing line to Early Access, Now Live, 3 days to go and Last chance. Blank means no offer.</t>
+          <t>One phrase everywhere: 'released in support of'. It goes in the opener unless the hook already names the beneficiary.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Action lines</t>
+          <t>Framing offer</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Three CTAs: get updates before launch, enter the draw for a draw, buy one for an open window. One deadline form: Closes {date} at {time} UK time, or 'until {time} on {weekday}, {date}' in an email.</t>
+          <t>A framing code on Inputs adds the first-purchase framing line to Early Access, Now Live, 3 days to go and Last chance. Blank means no offer.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Mechanic and window</t>
+          <t>Action lines</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Set mechanic to timed or draw and the sheet switches every line. For a timed edition, a 48-hour window gets the halfway email; a one-week window gets 5 days to go and 3 days to go.</t>
+          <t>Three CTAs: get updates before launch, enter the draw for a draw, buy one for an open window. One deadline form: Closes {date} at {time} UK time, or 'until {time} on {weekday}, {date}' in an email.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Mechanic and window</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Enter launch and close once as date and time; the sheet derives '30 April', '14:00 UK time', 'Thursday' and '07 May' where each email needs them.</t>
+          <t>Set mechanic to timed or draw and the sheet switches every line. For a timed edition, a 48-hour window gets the halfway email; a one-week window gets 5 days to go and 3 days to go.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>What stays written</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>A delay reason, a framing paragraph, editorial deep dives, the rest of the Monthly Preview, the artist's own email, artist-local times, and anything for a second release.</t>
+          <t>Enter launch and close once as date and time; the sheet derives '30 April', '14:00 UK time', 'Thursday' and '07 May' where each email needs them.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>What stays written</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>A delay reason, a framing paragraph, editorial deep dives, the rest of the Monthly Preview, the artist's own email, artist-local times, and anything for a second release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
           <t>How to use</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Fill the blue cells on Inputs. Read Posts, Tweets and Emails. To change the house wording, edit the blue cells on Lines once.</t>
         </is>

--- a/tool/release-copy-lucian-freud-tl-26.xlsx
+++ b/tool/release-copy-lucian-freud-tl-26.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -991,429 +991,446 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="64" customHeight="1">
+    <row r="35" ht="32" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>qualifier</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>spanning five decades of the artist's career</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>a few words after the edition phrase in the email opener, e.g. spanning five decades of the artist's career. Ten words at most, a phrase not a sentence, no we or our, no artist name, no beneficiary. Blank for none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
           <t>making</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>Each print was created in close collaboration with the Lucian Freud Estate by printmakers at Make-Ready, on 310gsm Hahnemühle German Etching paper, to faithfully preserve the texture, tonal depth and psychological intensity of the original paintings.</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>one sentence on how the edition was made; write 'printmakers at Make-Ready' and the sheet adds 'our'.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>quote</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>The difficulties of painting yourself are psychological, you've got to try to paint yourself as another person.</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>verbatim, a complete sentence, or blank</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Derived (formulas, do not edit)</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>named</t>
-        </is>
-      </c>
-      <c r="B39" s="10">
-        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
-        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>named_x</t>
+          <t>named</t>
         </is>
       </c>
       <c r="B40" s="10">
-        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
+        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>collab_x</t>
+          <t>named_x</t>
         </is>
       </c>
       <c r="B41" s="10">
-        <f>IF($B$5=$B$4,$B$40,$B$5)</f>
+        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>a_unit</t>
+          <t>collab_x</t>
         </is>
       </c>
       <c r="B42" s="10">
-        <f>IF(OR(LEFT($B$15,1)="a",LEFT($B$15,1)="e",LEFT($B$15,1)="i",LEFT($B$15,1)="o",LEFT($B$15,1)="u"),"an ","a ")&amp;$B$15</f>
+        <f>IF($B$5=$B$4,$B$41,$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>a_unit</t>
         </is>
       </c>
       <c r="B43" s="10">
-        <f>IF($B$12="yes","the "&amp;$B$11&amp;" series","‘"&amp;$B$11&amp;"’")</f>
+        <f>IF(OR(LEFT($B$15,1)="a",LEFT($B$15,1)="e",LEFT($B$15,1)="i",LEFT($B$15,1)="o",LEFT($B$15,1)="u"),"an ","a ")&amp;$B$15</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>work</t>
         </is>
       </c>
       <c r="B44" s="10">
-        <f>UPPER(LEFT($B$43,1))&amp;MID($B$43,2,999)</f>
+        <f>IF($B$12="yes","the "&amp;$B$11&amp;" series","‘"&amp;$B$11&amp;"’")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>work_email</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="B45" s="10">
-        <f>IF($B$12="yes","the "&amp;$B$11&amp;" series",$B$11)</f>
+        <f>UPPER(LEFT($B$44,1))&amp;MID($B$44,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Work_email</t>
+          <t>work_email</t>
         </is>
       </c>
       <c r="B46" s="10">
-        <f>UPPER(LEFT($B$45,1))&amp;MID($B$45,2,999)</f>
+        <f>IF($B$12="yes","the "&amp;$B$11&amp;" series",$B$11)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>work_intro</t>
+          <t>Work_email</t>
         </is>
       </c>
       <c r="B47" s="10">
-        <f>IF($B$12="yes",$B$13&amp;" from the "&amp;$B$11&amp;" series",IF($B$14=1,$B$11&amp;", "&amp;$B$13,$B$13))</f>
+        <f>UPPER(LEFT($B$46,1))&amp;MID($B$46,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>work_intro</t>
         </is>
       </c>
       <c r="B48" s="10">
-        <f>IF(OR($B$20="",$B$51),"",", released in support of "&amp;$B$20)</f>
+        <f>IF($B$14=1,$B$11&amp;", ","")&amp;$B$13&amp;IF($B$35="","",IF(LEFT($B$35,1)=",",""," ")&amp;$B$35)</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>support</t>
+        </is>
+      </c>
+      <c r="B49" s="10">
+        <f>IF(OR($B$20="",$B$52),"",", released in support of "&amp;$B$20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
           <t>beneficiary_tagged</t>
         </is>
       </c>
-      <c r="B49" s="10">
+      <c r="B50" s="10">
         <f>IF($B$20="","",$B$20&amp;IF($B$21="",""," (@"&amp;$B$21&amp;")"))</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="80" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="51" ht="80" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>bio_tagged</t>
         </is>
       </c>
-      <c r="B50" s="10">
-        <f>IF($B$6="",$B$33,SUBSTITUTE($B$33,$B$4,$B$39,1))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>hook_names_beneficiary</t>
-        </is>
-      </c>
       <c r="B51" s="10">
-        <f>IF($B$20="",FALSE,ISNUMBER(SEARCH($B$20,$B$34)))</f>
+        <f>IF($B$6="",$B$33,SUBSTITUTE($B$33,$B$4,$B$40,1))</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>hook_names_beneficiary</t>
+        </is>
+      </c>
+      <c r="B52" s="10">
+        <f>IF($B$20="",FALSE,ISNUMBER(SEARCH($B$20,$B$34)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>features</t>
         </is>
       </c>
-      <c r="B52" s="10">
+      <c r="B53" s="10">
         <f>$B$26&amp;IF($B$27="","",". "&amp;$B$27)&amp;IF($B$28="","",". "&amp;$B$28)&amp;IF($B$29="","",". "&amp;$B$29)&amp;IF($B$30="","",". "&amp;$B$30)&amp;"."</f>
         <v/>
       </c>
     </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>features_list</t>
         </is>
       </c>
-      <c r="B53" s="10">
+      <c r="B54" s="10">
         <f>"· "&amp;$B$26&amp;IF($B$27="","",CHAR(10)&amp;"· "&amp;$B$27)&amp;IF($B$28="","",CHAR(10)&amp;"· "&amp;$B$28)&amp;IF($B$29="","",CHAR(10)&amp;"· "&amp;$B$29)&amp;IF($B$30="","",CHAR(10)&amp;"· "&amp;$B$30)</f>
         <v/>
       </c>
     </row>
-    <row r="54" ht="70" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="55" ht="70" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>features_list_support</t>
         </is>
       </c>
-      <c r="B54" s="10">
-        <f>$B$53&amp;IF(OR($B$20="",$B$51),"",CHAR(10)&amp;"· Released in support of "&amp;$B$20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>making_ours</t>
-        </is>
-      </c>
       <c r="B55" s="10">
-        <f>SUBSTITUTE($B$35,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
+        <f>$B$54&amp;IF(OR($B$20="",$B$52),"",CHAR(10)&amp;"· Released in support of "&amp;$B$20)</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>making_ours_tagged</t>
+          <t>making_ours</t>
         </is>
       </c>
       <c r="B56" s="10">
-        <f>SUBSTITUTE($B$35,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
+        <f>SUBSTITUTE($B$36,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>launch_date</t>
+          <t>making_ours_tagged</t>
         </is>
       </c>
       <c r="B57" s="10">
-        <f>TEXT($B$18,"d mmmm")</f>
+        <f>SUBSTITUTE($B$36,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>launch_time</t>
+          <t>launch_date</t>
         </is>
       </c>
       <c r="B58" s="10">
-        <f>TEXT($B$18,"hh:mm")&amp;" UK time"</f>
+        <f>TEXT($B$18,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>launch_weekday</t>
+          <t>launch_time</t>
         </is>
       </c>
       <c r="B59" s="10">
-        <f>TEXT($B$18,"dddd")</f>
+        <f>TEXT($B$18,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>launch_date_dd</t>
+          <t>launch_weekday</t>
         </is>
       </c>
       <c r="B60" s="10">
-        <f>TEXT($B$18,"dd mmmm")</f>
+        <f>TEXT($B$18,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>close_date</t>
+          <t>launch_date_dd</t>
         </is>
       </c>
       <c r="B61" s="10">
-        <f>TEXT($B$19,"d mmmm")</f>
+        <f>TEXT($B$18,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>close_time</t>
+          <t>close_date</t>
         </is>
       </c>
       <c r="B62" s="10">
-        <f>TEXT($B$19,"hh:mm")&amp;" UK time"</f>
+        <f>TEXT($B$19,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>close_weekday</t>
+          <t>close_time</t>
         </is>
       </c>
       <c r="B63" s="10">
-        <f>TEXT($B$19,"dddd")</f>
+        <f>TEXT($B$19,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>close_date_dd</t>
+          <t>close_weekday</t>
         </is>
       </c>
       <c r="B64" s="10">
-        <f>TEXT($B$19,"dd mmmm")</f>
+        <f>TEXT($B$19,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>collect_phrase</t>
+          <t>close_date_dd</t>
         </is>
       </c>
       <c r="B65" s="10">
-        <f>SUBSTITUTE($B$13," new "," ",1)</f>
+        <f>TEXT($B$19,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>edition_phrase_cap</t>
+          <t>collect_phrase</t>
         </is>
       </c>
       <c r="B66" s="10">
-        <f>UPPER(LEFT($B$13,1))&amp;MID($B$13,2,999)</f>
+        <f>SUBSTITUTE($B$13," new "," ",1)</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>window_cap</t>
+          <t>edition_phrase_cap</t>
         </is>
       </c>
       <c r="B67" s="10">
-        <f>UPPER(LEFT($B$17,1))&amp;MID($B$17,2,999)</f>
+        <f>UPPER(LEFT($B$13,1))&amp;MID($B$13,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>card_line</t>
+          <t>window_cap</t>
         </is>
       </c>
       <c r="B68" s="10">
-        <f>$B$66&amp;" by "&amp;$B$4&amp;"."</f>
+        <f>UPPER(LEFT($B$17,1))&amp;MID($B$17,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>card_line</t>
         </is>
       </c>
       <c r="B69" s="10">
-        <f>IF($B$12="yes","Untitled",$B$11)&amp;CHAR(10)&amp;$B$68</f>
+        <f>$B$67&amp;" by "&amp;$B$4&amp;"."</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>quote_line</t>
+          <t>card</t>
         </is>
       </c>
       <c r="B70" s="10">
-        <f>IF($B$36="","","“"&amp;$B$36&amp;"” – "&amp;$B$4)</f>
+        <f>IF($B$12="yes","Untitled",$B$11)&amp;CHAR(10)&amp;$B$69</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>each_artwork</t>
+          <t>quote_line</t>
         </is>
       </c>
       <c r="B71" s="10">
-        <f>IF($B$14&gt;1," for each artwork","")</f>
+        <f>IF($B$37="","","“"&amp;$B$37&amp;"” – "&amp;$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>work_word</t>
+          <t>each_artwork</t>
         </is>
       </c>
       <c r="B72" s="10">
-        <f>IF($B$14&gt;1,"works","work")</f>
+        <f>IF($B$14&gt;1," for each artwork","")</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
+          <t>work_word</t>
+        </is>
+      </c>
+      <c r="B73" s="10">
+        <f>IF($B$14&gt;1,"works","work")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
           <t>add_what</t>
         </is>
       </c>
-      <c r="B73" s="10">
-        <f>IF($B$14&gt;1,$B$42,$B$45)</f>
+      <c r="B74" s="10">
+        <f>IF($B$14&gt;1,$B$43,$B$46)</f>
         <v/>
       </c>
     </row>
@@ -1502,7 +1519,7 @@
         </is>
       </c>
       <c r="C6" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$39),"{work}",Inputs!$B$43),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44),"{edition_phrase}",Inputs!$B$13)</f>
         <v/>
       </c>
     </row>
@@ -1518,7 +1535,7 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$39),"{work}",Inputs!$B$43),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44),"{edition_phrase}",Inputs!$B$13)</f>
         <v/>
       </c>
     </row>
@@ -1534,7 +1551,7 @@
         </is>
       </c>
       <c r="C8" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$39),"{work}",Inputs!$B$43),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44),"{edition_phrase}",Inputs!$B$13)</f>
         <v/>
       </c>
     </row>
@@ -1550,7 +1567,7 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$36)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$37)</f>
         <v/>
       </c>
     </row>
@@ -1566,7 +1583,7 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$39),"{Work}",Inputs!$B$44),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$40),"{Work}",Inputs!$B$45),"{edition_phrase}",Inputs!$B$13)</f>
         <v/>
       </c>
     </row>
@@ -1582,7 +1599,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$39),"{Work}",Inputs!$B$44),"{window}",Inputs!$B$17)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$40),"{Work}",Inputs!$B$45),"{window}",Inputs!$B$17)</f>
         <v/>
       </c>
     </row>
@@ -1598,7 +1615,7 @@
         </is>
       </c>
       <c r="C12" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$39),"{work}",Inputs!$B$43)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44)</f>
         <v/>
       </c>
     </row>
@@ -1614,7 +1631,7 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$39),"{work}",Inputs!$B$43)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44)</f>
         <v/>
       </c>
     </row>
@@ -1630,7 +1647,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$39),"{work}",Inputs!$B$43)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44)</f>
         <v/>
       </c>
     </row>
@@ -1646,7 +1663,7 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$52)</f>
+        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$53)</f>
         <v/>
       </c>
     </row>
@@ -1662,7 +1679,7 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$49)</f>
+        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$50)</f>
         <v/>
       </c>
     </row>
@@ -1678,7 +1695,7 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$17),"{launch_date}",Inputs!$B$57),"{launch_time}",Inputs!$B$58)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$17),"{launch_date}",Inputs!$B$58),"{launch_time}",Inputs!$B$59)</f>
         <v/>
       </c>
     </row>
@@ -1694,7 +1711,7 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$61),"{close_time}",Inputs!$B$62)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1727,7 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$42),"{close_date}",Inputs!$B$61),"{close_time}",Inputs!$B$62)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$43),"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -1726,7 +1743,7 @@
         </is>
       </c>
       <c r="C20" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$61),"{close_time}",Inputs!$B$62)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -1781,7 +1798,7 @@
         </is>
       </c>
       <c r="C24" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$41),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$42),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -1829,7 +1846,7 @@
         </is>
       </c>
       <c r="C27" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{link}",Inputs!$B$8),"{window}",Inputs!$B$17),"{launch_date}",Inputs!$B$57),"{launch_time}",Inputs!$B$58)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{link}",Inputs!$B$8),"{window}",Inputs!$B$17),"{launch_date}",Inputs!$B$58),"{launch_time}",Inputs!$B$59)</f>
         <v/>
       </c>
     </row>
@@ -1845,7 +1862,7 @@
         </is>
       </c>
       <c r="C28" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$61),"{close_time}",Inputs!$B$62)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -1861,7 +1878,7 @@
         </is>
       </c>
       <c r="C29" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$42),"{close_date}",Inputs!$B$61),"{close_time}",Inputs!$B$62)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$43),"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -1916,7 +1933,7 @@
         </is>
       </c>
       <c r="C33" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B33,"{close_date}",Inputs!$B$61),"{close_time}",Inputs!$B$62)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B33,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -1948,7 +1965,7 @@
         </is>
       </c>
       <c r="C35" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B35,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$42)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B35,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$43)</f>
         <v/>
       </c>
     </row>
@@ -2003,7 +2020,7 @@
         </is>
       </c>
       <c r="C39" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B39,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$66)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B39,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -2019,7 +2036,7 @@
         </is>
       </c>
       <c r="C40" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$47),"{support}",Inputs!$B$48),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2035,7 +2052,7 @@
         </is>
       </c>
       <c r="C41" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$58),"{launch_weekday}",Inputs!$B$59),"{launch_date_dd}",Inputs!$B$60)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59),"{launch_weekday}",Inputs!$B$60),"{launch_date_dd}",Inputs!$B$61)</f>
         <v/>
       </c>
     </row>
@@ -2145,7 +2162,7 @@
         </is>
       </c>
       <c r="C49" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$58)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59)</f>
         <v/>
       </c>
     </row>
@@ -2209,7 +2226,7 @@
         </is>
       </c>
       <c r="C53" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$47),"{support}",Inputs!$B$48),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2225,7 +2242,7 @@
         </is>
       </c>
       <c r="C54" s="10">
-        <f>SUBSTITUTE(B54,"{launch_date}",Inputs!$B$57)</f>
+        <f>SUBSTITUTE(B54,"{launch_date}",Inputs!$B$58)</f>
         <v/>
       </c>
     </row>
@@ -2257,7 +2274,7 @@
         </is>
       </c>
       <c r="C56" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$47),"{support}",Inputs!$B$48),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2273,7 +2290,7 @@
         </is>
       </c>
       <c r="C57" s="10">
-        <f>SUBSTITUTE(B57,"{launch_date}",Inputs!$B$57)</f>
+        <f>SUBSTITUTE(B57,"{launch_date}",Inputs!$B$58)</f>
         <v/>
       </c>
     </row>
@@ -2289,7 +2306,7 @@
         </is>
       </c>
       <c r="C58" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B58,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$58)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B58,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59)</f>
         <v/>
       </c>
     </row>
@@ -2362,7 +2379,7 @@
         </is>
       </c>
       <c r="C63" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B63,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$47),"{support}",Inputs!$B$48),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$17)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B63,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$17)</f>
         <v/>
       </c>
     </row>
@@ -2378,7 +2395,7 @@
         </is>
       </c>
       <c r="C64" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{close_time}",Inputs!$B$62),"{close_weekday}",Inputs!$B$63),"{close_date_dd}",Inputs!$B$64),"{add_what}",Inputs!$B$73)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65),"{add_what}",Inputs!$B$74)</f>
         <v/>
       </c>
     </row>
@@ -2410,7 +2427,7 @@
         </is>
       </c>
       <c r="C66" s="10">
-        <f>SUBSTITUTE(B66,"{a_unit}",Inputs!$B$42)</f>
+        <f>SUBSTITUTE(B66,"{a_unit}",Inputs!$B$43)</f>
         <v/>
       </c>
     </row>
@@ -2458,7 +2475,7 @@
         </is>
       </c>
       <c r="C69" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$66)</f>
         <v/>
       </c>
     </row>
@@ -2474,7 +2491,7 @@
         </is>
       </c>
       <c r="C70" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$62),"{close_weekday}",Inputs!$B$63),"{close_date_dd}",Inputs!$B$64)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -2490,7 +2507,7 @@
         </is>
       </c>
       <c r="C71" s="10">
-        <f>SUBSTITUTE(B71,"{a_unit}",Inputs!$B$42)</f>
+        <f>SUBSTITUTE(B71,"{a_unit}",Inputs!$B$43)</f>
         <v/>
       </c>
     </row>
@@ -2513,7 +2530,7 @@
         </is>
       </c>
       <c r="C73" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$65),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$62),"{close_weekday}",Inputs!$B$63),"{close_date_dd}",Inputs!$B$64)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$66),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -2529,7 +2546,7 @@
         </is>
       </c>
       <c r="C74" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B74,"{each_artwork}",Inputs!$B$71),"{work_word}",Inputs!$B$72)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B74,"{each_artwork}",Inputs!$B$72),"{work_word}",Inputs!$B$73)</f>
         <v/>
       </c>
     </row>
@@ -2545,7 +2562,7 @@
         </is>
       </c>
       <c r="C75" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$45),"{collect_phrase}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$46),"{collect_phrase}",Inputs!$B$66)</f>
         <v/>
       </c>
     </row>
@@ -2561,7 +2578,7 @@
         </is>
       </c>
       <c r="C76" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{close_time}",Inputs!$B$62),"{close_weekday}",Inputs!$B$63),"{close_date_dd}",Inputs!$B$64)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -2751,7 +2768,7 @@
         </is>
       </c>
       <c r="C89" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$47),"{support}",Inputs!$B$48)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49)</f>
         <v/>
       </c>
     </row>
@@ -2767,7 +2784,7 @@
         </is>
       </c>
       <c r="C90" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B90,"{close_date}",Inputs!$B$61),"{close_time}",Inputs!$B$62)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B90,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -2783,7 +2800,7 @@
         </is>
       </c>
       <c r="C91" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$58),"{launch_weekday}",Inputs!$B$59),"{launch_date_dd}",Inputs!$B$60)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59),"{launch_weekday}",Inputs!$B$60),"{launch_date_dd}",Inputs!$B$61)</f>
         <v/>
       </c>
     </row>
@@ -2909,7 +2926,7 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>Inputs!$B$50</f>
+        <f>Inputs!$B$51</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -2961,7 +2978,7 @@
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$51,"",IF(Inputs!$B$49="",""," "&amp;Lines!$C$16))</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$52,"",IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H5" s="11">
@@ -3005,11 +3022,11 @@
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>Inputs!$B$56</f>
+        <f>Inputs!$B$57</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$49="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H6" s="11">
@@ -3049,19 +3066,19 @@
         </is>
       </c>
       <c r="E7" s="11">
-        <f>IF(Inputs!$B$36="","(no quote given, post skipped)",Lines!$C$9)</f>
+        <f>IF(Inputs!$B$37="","(no quote given, post skipped)",Lines!$C$9)</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>IF(Inputs!$B$36="","",Lines!$C$10)</f>
+        <f>IF(Inputs!$B$37="","",Lines!$C$10)</f>
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>IF(Inputs!$B$36="","",Lines!$C$15&amp;IF(Inputs!$B$49="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$37="","",Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H7" s="11">
-        <f>IF(Inputs!$B$36="","",IF(Inputs!$B$16="draw",Lines!$C$18,Lines!$C$17))</f>
+        <f>IF(Inputs!$B$37="","",IF(Inputs!$B$16="draw",Lines!$C$18,Lines!$C$17))</f>
         <v/>
       </c>
       <c r="I7" s="11">
@@ -3069,7 +3086,7 @@
         <v/>
       </c>
       <c r="J7" s="11">
-        <f>IF(Inputs!$B$36="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
+        <f>IF(Inputs!$B$37="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
         <v/>
       </c>
       <c r="K7" s="11">
@@ -3105,7 +3122,7 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IF(Inputs!$B$16="draw","",Lines!$C$15&amp;IF(Inputs!$B$49="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$16="draw","",Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H8" s="11">
@@ -3153,7 +3170,7 @@
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>IF(Inputs!$B$16="draw","",Lines!$C$15&amp;IF(Inputs!$B$49="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$16="draw","",Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H9" s="11">
@@ -3201,7 +3218,7 @@
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$49="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H10" s="11">
@@ -3361,7 +3378,7 @@
         </is>
       </c>
       <c r="D5" s="11">
-        <f>SUBSTITUTE(IF(Inputs!$B$12="yes",Lines!$C$7,Lines!$C$6),Inputs!$B$39,Inputs!$B$40)</f>
+        <f>SUBSTITUTE(IF(Inputs!$B$12="yes",Lines!$C$7,Lines!$C$6),Inputs!$B$40,Inputs!$B$41)</f>
         <v/>
       </c>
       <c r="E5" s="11">
@@ -3369,7 +3386,7 @@
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>IF(OR(Inputs!$B$20="",Inputs!$B$51),"",Lines!$C$26)</f>
+        <f>IF(OR(Inputs!$B$20="",Inputs!$B$52),"",Lines!$C$26)</f>
         <v/>
       </c>
       <c r="G5" s="11">
@@ -3400,7 +3417,7 @@
         </is>
       </c>
       <c r="D6" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$39,Inputs!$B$40))</f>
+        <f>IF(Inputs!$B$16="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$40,Inputs!$B$41))</f>
         <v/>
       </c>
       <c r="E6" s="11">
@@ -3439,7 +3456,7 @@
         </is>
       </c>
       <c r="D7" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$39,Inputs!$B$40))</f>
+        <f>IF(Inputs!$B$16="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$40,Inputs!$B$41))</f>
         <v/>
       </c>
       <c r="E7" s="11">
@@ -3478,7 +3495,7 @@
         </is>
       </c>
       <c r="D8" s="11">
-        <f>IF(Inputs!$B$16="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$39,Inputs!$B$40),SUBSTITUTE(Lines!$C$13,Inputs!$B$39,Inputs!$B$40))</f>
+        <f>IF(Inputs!$B$16="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$40,Inputs!$B$41),SUBSTITUTE(Lines!$C$13,Inputs!$B$40,Inputs!$B$41))</f>
         <v/>
       </c>
       <c r="E8" s="11">
@@ -3647,19 +3664,19 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$61&amp;".","Launching "&amp;Inputs!$B$57&amp;". Register for updates."))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$62&amp;".","Launching "&amp;Inputs!$B$58&amp;". Register for updates."))</f>
         <v/>
       </c>
       <c r="G4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw","Launching "&amp;Inputs!$B$57))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw","Launching "&amp;Inputs!$B$58))</f>
         <v/>
       </c>
       <c r="H4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw",Inputs!$B$46,Inputs!$B$46&amp;" by "&amp;Inputs!$B$4))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw",Inputs!$B$47,Inputs!$B$47&amp;" by "&amp;Inputs!$B$4))</f>
         <v/>
       </c>
       <c r="I4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$40&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Inputs!$B$53="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$53)&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42))))))</f>
+        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$40&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(Inputs!$B$54="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$54)&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42))))))</f>
         <v/>
       </c>
       <c r="J4" s="11">
@@ -3667,15 +3684,15 @@
         <v/>
       </c>
       <c r="K4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$69)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$70)</f>
         <v/>
       </c>
       <c r="L4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$71)</f>
         <v/>
       </c>
       <c r="M4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Collect "&amp;Inputs!$B$65,"Launching "&amp;Inputs!$B$57))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Collect "&amp;Inputs!$B$66,"Launching "&amp;Inputs!$B$58))</f>
         <v/>
       </c>
       <c r="N4" s="11">
@@ -3785,7 +3802,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$54="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$54)&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$36))&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)))</f>
+        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$36))&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)))</f>
         <v/>
       </c>
       <c r="J6" s="11">
@@ -3848,7 +3865,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$54="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$54)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
+        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
         <v/>
       </c>
       <c r="J7" s="11">
@@ -3856,7 +3873,7 @@
         <v/>
       </c>
       <c r="K7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$69)</f>
+        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$70)</f>
         <v/>
       </c>
       <c r="L7" s="11">
@@ -3919,7 +3936,7 @@
         <v/>
       </c>
       <c r="K8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$69)</f>
+        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$70)</f>
         <v/>
       </c>
       <c r="L8" s="11">
@@ -3982,7 +3999,7 @@
         <v/>
       </c>
       <c r="K9" s="11">
-        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$69)</f>
+        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$70)</f>
         <v/>
       </c>
       <c r="L9" s="11">
@@ -4025,7 +4042,7 @@
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$67&amp;", starting now.")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$68&amp;", starting now.")</f>
         <v/>
       </c>
       <c r="G10" s="11">
@@ -4033,11 +4050,11 @@
         <v/>
       </c>
       <c r="H10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$67&amp;", starting now")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$68&amp;", starting now")</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$63&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Inputs!$B$54="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$54)&amp;IF(Lines!$C$64="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$64)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$36))))</f>
+        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$63&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Lines!$C$64="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$64)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$36))))</f>
         <v/>
       </c>
       <c r="J10" s="11">
@@ -4045,15 +4062,15 @@
         <v/>
       </c>
       <c r="K10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$69)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$70)</f>
         <v/>
       </c>
       <c r="L10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$71)</f>
         <v/>
       </c>
       <c r="M10" s="11">
-        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$65)</f>
+        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$66)</f>
         <v/>
       </c>
       <c r="N10" s="11">
@@ -4167,7 +4184,7 @@
         <v/>
       </c>
       <c r="J12" s="11">
-        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$42)</f>
+        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$43)</f>
         <v/>
       </c>
       <c r="K12" s="11">
@@ -4218,7 +4235,7 @@
         <v/>
       </c>
       <c r="G13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$46&amp;" by "&amp;Inputs!$B$4)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$47&amp;" by "&amp;Inputs!$B$4)</f>
         <v/>
       </c>
       <c r="H13" s="11">
@@ -4230,11 +4247,11 @@
         <v/>
       </c>
       <c r="J13" s="11">
-        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$42)</f>
+        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$43)</f>
         <v/>
       </c>
       <c r="K13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$69)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$70)</f>
         <v/>
       </c>
       <c r="L13" s="11">
@@ -4277,7 +4294,7 @@
         <v/>
       </c>
       <c r="F14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$16="draw","The draw closes at "&amp;Inputs!$B$62&amp;" on "&amp;Inputs!$B$61&amp;".","Time is almost up."))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$16="draw","The draw closes at "&amp;Inputs!$B$63&amp;" on "&amp;Inputs!$B$62&amp;".","Time is almost up."))</f>
         <v/>
       </c>
       <c r="G14" s="11">
@@ -4297,7 +4314,7 @@
         <v/>
       </c>
       <c r="K14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$69)</f>
+        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$70)</f>
         <v/>
       </c>
       <c r="L14" s="11">
@@ -4478,7 +4495,7 @@
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$89&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$90,Lines!$C$91)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$90,Lines!$C$91))))</f>
+        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$89&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$90,Lines!$C$91)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$90,Lines!$C$91))))</f>
         <v/>
       </c>
       <c r="J17" s="11">
@@ -4599,7 +4616,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>The opener names the work only for a single print: 'The Changeling, a new limited edition print'. A pair or a quartet is just the edition phrase, and the hook names the work; many sets have no collective name anyway. Untitled works from a named series read 'six new limited edition prints from the Dream House series'.</t>
+          <t>The opener's tail is the title (single print only), the edition phrase, and the qualifier if one is written: 'The Changeling, a new limited edition print'; 'a quartet of new limited edition prints spanning five decades of the artist's career'; 'six new limited edition prints from his iconic Dream House series'. A pair or a quartet takes no title; the hook names the work. The same tail is used by the Insiders email, LE early access, Now Live and the Monthly Preview paragraph.</t>
         </is>
       </c>
     </row>

--- a/tool/release-copy-lucian-freud-tl-26.xlsx
+++ b/tool/release-copy-lucian-freud-tl-26.xlsx
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -641,7 +641,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>title_1</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -651,485 +651,489 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>exactly as it appears, shared by the set if there is one; for untitled works from a named series, the series name</t>
+          <t>exactly as it appears; the set's one title if it has one; for untitled works from a named series, the series name</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>is_series</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>title_2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>yes only for untitled works from a named series</t>
+          <t>for a pair or a trio with their own titles; blank otherwise</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>edition_phrase</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>a quartet of new limited edition prints</t>
-        </is>
-      </c>
+          <t>title_3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>e.g. a new limited edition print; a quartet of new limited edition embroideries; a new limited edition print in four colourways</t>
+          <t>blank otherwise. More than three titled works: give the set a collective title, or use the templates</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>works</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="n">
-        <v>4</v>
+          <t>is_series</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>number of artworks: sets the plural wording</t>
+          <t>yes only for untitled works from a named series</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>edition_phrase</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>print</t>
+          <t>a quartet of new limited edition prints</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>what one is called: print, embroidery, sculpture, edition</t>
+          <t>e.g. a new limited edition print; a quartet of new limited edition embroideries; a new limited edition print in four colourways</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>mechanic</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>timed</t>
-        </is>
+          <t>works</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4</v>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>timed (TL) or draw (LE)</t>
+          <t>number of artworks: sets the plural wording</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>48 hours</t>
+          <t>print</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>48 hours or one week; timed only</t>
+          <t>what one is called: print, embroidery, sculpture, edition</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>launch_at</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>46126.58333333334</v>
+          <t>mechanic</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>timed</t>
+        </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>date and time the window opens, or the draw opens (UK)</t>
+          <t>timed (TL) or draw (LE)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>closes_at</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>46128.58333333334</v>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>48 hours</t>
+        </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>date and time the window or draw closes (UK)</t>
+          <t>48 hours or one week; timed only</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>beneficiary</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr"/>
+          <t>launch_at</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>46126.58333333334</v>
+      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>as it reads mid-sentence; blank if none</t>
+          <t>date and time the window opens, or the draw opens (UK)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>beneficiary_handle</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr"/>
+          <t>closes_at</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>46128.58333333334</v>
+      </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>blank if none</t>
+          <t>date and time the window or draw closes (UK)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>advisor</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>Curtis</t>
-        </is>
-      </c>
+          <t>beneficiary</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>signs the Insiders email and the first-time collector survey: Sofiya, Curtis or Sam</t>
+          <t>as it reads mid-sentence; blank if none</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>early_access_code</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>000-000</t>
-        </is>
-      </c>
+          <t>beneficiary_handle</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>draw releases</t>
+          <t>blank if none</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>framing_code</t>
+          <t>advisor</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Freud-0426-10</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>first-purchase framing offer code, e.g. Freud-0426-10; blank for no offer</t>
+          <t>signs the Insiders email and the first-time collector survey: Sofiya, Curtis or Sam</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>framing_percent</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>10</v>
+          <t>early_access_code</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>000-000</t>
+        </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>10 or 20</t>
+          <t>draw releases</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>feature_1</t>
+          <t>framing_code</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Individually numbered</t>
+          <t>Freud-0426-10</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>the standard three; clear a cell to drop it</t>
+          <t>first-purchase framing offer code, e.g. Freud-0426-10; blank for no offer</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>feature_2</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Free worldwide shipping</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
+          <t>framing_percent</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>10 or 20</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>feature_3</t>
+          <t>feature_1</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Created in collaboration with the Lucian Freud Estate and Bridgeman Images</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr"/>
+          <t>Individually numbered</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>the standard three; clear a cell to drop it</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>feature_4</t>
+          <t>feature_2</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Available individually, as curated pairs or as a complete quartet</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>bespoke, e.g. Hand-finished by the artist. Never 'our'.</t>
-        </is>
-      </c>
+          <t>Free worldwide shipping</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>feature_3</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Created in collaboration with the Lucian Freud Estate and Bridgeman Images</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>feature_4</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Available individually, as curated pairs or as a complete quartet</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>bespoke, e.g. Hand-finished by the artist. Never 'our'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>feature_5</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>bespoke, e.g. Available individually or as a set</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Fragments, written once per release. Voice-neutral: no we or our, no artist name in the hook or making line.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>bio</t>
         </is>
       </c>
-      <c r="B33" s="8" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Lucian Freud (1922–2011) built his reputation painting people exactly as he saw them. Working from life, often over months of sittings, he turned hours of looking into raw studies of flesh, time and psychological tension.</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>2 to 3 sentences on the artist, third person, no handle. Coming Soon post only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="64" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>hook</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Portraits, 1952–2002 brings together four seminal works spanning five decades of Freud's uncompromising portrait practice, from early intimacy to late self-scrutiny. The quartet is Girl in Bed, 1953; Reflection with Two Children (Self-Portrait), 1965; Double Portrait, 1988–90; and Self-Portrait (Reflection), 2002.</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>1 to 2 sentences about the work only. Reused in every post and email.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>qualifier</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>spanning five decades of the artist's career</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>a few words after the edition phrase in the email opener, e.g. spanning five decades of the artist's career. Ten words at most, a phrase not a sentence, no we or our, no artist name, no beneficiary. Blank for none.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="64" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>making</t>
+          <t>hook</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Each print was created in close collaboration with the Lucian Freud Estate by printmakers at Make-Ready, on 310gsm Hahnemühle German Etching paper, to faithfully preserve the texture, tonal depth and psychological intensity of the original paintings.</t>
+          <t>Portraits, 1952–2002 brings together four seminal works spanning five decades of Freud's uncompromising portrait practice, from early intimacy to late self-scrutiny. The quartet is Girl in Bed, 1953; Reflection with Two Children (Self-Portrait), 1965; Double Portrait, 1988–90; and Self-Portrait (Reflection), 2002.</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>one sentence on how the edition was made; write 'printmakers at Make-Ready' and the sheet adds 'our'.</t>
+          <t>1 to 2 sentences about the work only. Reused in every post and email.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
+          <t>qualifier</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>spanning five decades of the artist's career</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>a few words after the edition phrase in the email opener, e.g. spanning five decades of the artist's career. Ten words at most, a phrase not a sentence, no we or our, no artist name, no beneficiary. Blank for none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>making</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Each print was created in close collaboration with the Lucian Freud Estate by printmakers at Make-Ready, on 310gsm Hahnemühle German Etching paper, to faithfully preserve the texture, tonal depth and psychological intensity of the original paintings.</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>one sentence on how the edition was made; write 'printmakers at Make-Ready' and the sheet adds 'our'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
           <t>quote</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>The difficulties of painting yourself are psychological, you've got to try to paint yourself as another person.</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>verbatim, a complete sentence, or blank</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Derived (formulas, do not edit)</t>
         </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>named</t>
-        </is>
-      </c>
-      <c r="B40" s="10">
-        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>named_x</t>
-        </is>
-      </c>
-      <c r="B41" s="10">
-        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
-        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>collab_x</t>
+          <t>named</t>
         </is>
       </c>
       <c r="B42" s="10">
-        <f>IF($B$5=$B$4,$B$41,$B$5)</f>
+        <f>$B$4&amp;IF($B$6="",""," (@"&amp;$B$6&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>a_unit</t>
+          <t>named_x</t>
         </is>
       </c>
       <c r="B43" s="10">
-        <f>IF(OR(LEFT($B$15,1)="a",LEFT($B$15,1)="e",LEFT($B$15,1)="i",LEFT($B$15,1)="o",LEFT($B$15,1)="u"),"an ","a ")&amp;$B$15</f>
+        <f>$B$4&amp;IF($B$7="",""," (@"&amp;$B$7&amp;")")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>work</t>
+          <t>collab_x</t>
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IF($B$12="yes","the "&amp;$B$11&amp;" series","‘"&amp;$B$11&amp;"’")</f>
+        <f>IF($B$5=$B$4,$B$43,$B$5)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Work</t>
+          <t>a_unit</t>
         </is>
       </c>
       <c r="B45" s="10">
-        <f>UPPER(LEFT($B$44,1))&amp;MID($B$44,2,999)</f>
+        <f>IF(OR(LEFT($B$17,1)="a",LEFT($B$17,1)="e",LEFT($B$17,1)="i",LEFT($B$17,1)="o",LEFT($B$17,1)="u"),"an ","a ")&amp;$B$17</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>work_email</t>
+          <t>work</t>
         </is>
       </c>
       <c r="B46" s="10">
-        <f>IF($B$12="yes","the "&amp;$B$11&amp;" series",$B$11)</f>
+        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="","‘"&amp;$B$11&amp;"’",IF($B$13="","‘"&amp;$B$11&amp;"’ and ‘"&amp;$B$12&amp;"’","‘"&amp;$B$11&amp;"’, ‘"&amp;$B$12&amp;"’ and ‘"&amp;$B$13&amp;"’")))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Work_email</t>
+          <t>Work</t>
         </is>
       </c>
       <c r="B47" s="10">
@@ -1140,297 +1144,319 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>work_intro</t>
+          <t>work_email</t>
         </is>
       </c>
       <c r="B48" s="10">
-        <f>IF($B$14=1,$B$11&amp;", ","")&amp;$B$13&amp;IF($B$35="","",IF(LEFT($B$35,1)=",",""," ")&amp;$B$35)</f>
+        <f>IF($B$14="yes","the "&amp;$B$11&amp;" series",IF($B$12="",$B$11,IF($B$13="",$B$11&amp;" and "&amp;$B$12,$B$11&amp;", "&amp;$B$12&amp;" and "&amp;$B$13)))</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>Work_email</t>
         </is>
       </c>
       <c r="B49" s="10">
-        <f>IF(OR($B$20="",$B$52),"",", released in support of "&amp;$B$20)</f>
+        <f>UPPER(LEFT($B$48,1))&amp;MID($B$48,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>beneficiary_tagged</t>
+          <t>work_intro</t>
         </is>
       </c>
       <c r="B50" s="10">
-        <f>IF($B$20="","",$B$20&amp;IF($B$21="",""," (@"&amp;$B$21&amp;")"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="80" customHeight="1">
+        <f>IF($B$16=1,$B$11&amp;", ","")&amp;$B$15&amp;IF($B$37="","",IF(LEFT($B$37,1)=",",""," ")&amp;$B$37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>bio_tagged</t>
+          <t>support</t>
         </is>
       </c>
       <c r="B51" s="10">
-        <f>IF($B$6="",$B$33,SUBSTITUTE($B$33,$B$4,$B$40,1))</f>
+        <f>IF(OR($B$22="",$B$54),"",", released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>beneficiary_tagged</t>
+        </is>
+      </c>
+      <c r="B52" s="10">
+        <f>IF($B$22="","",$B$22&amp;IF($B$23="",""," (@"&amp;$B$23&amp;")"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="80" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>bio_tagged</t>
+        </is>
+      </c>
+      <c r="B53" s="10">
+        <f>IF($B$6="",$B$35,SUBSTITUTE($B$35,$B$4,$B$42,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>hook_names_beneficiary</t>
         </is>
       </c>
-      <c r="B52" s="10">
-        <f>IF($B$20="",FALSE,ISNUMBER(SEARCH($B$20,$B$34)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="B54" s="10">
+        <f>IF($B$22="",FALSE,ISNUMBER(SEARCH($B$22,$B$36)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>features</t>
         </is>
       </c>
-      <c r="B53" s="10">
-        <f>$B$26&amp;IF($B$27="","",". "&amp;$B$27)&amp;IF($B$28="","",". "&amp;$B$28)&amp;IF($B$29="","",". "&amp;$B$29)&amp;IF($B$30="","",". "&amp;$B$30)&amp;"."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="B55" s="10">
+        <f>$B$28&amp;IF($B$29="","",". "&amp;$B$29)&amp;IF($B$30="","",". "&amp;$B$30)&amp;IF($B$31="","",". "&amp;$B$31)&amp;IF($B$32="","",". "&amp;$B$32)&amp;"."</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>features_list</t>
         </is>
       </c>
-      <c r="B54" s="10">
-        <f>"· "&amp;$B$26&amp;IF($B$27="","",CHAR(10)&amp;"· "&amp;$B$27)&amp;IF($B$28="","",CHAR(10)&amp;"· "&amp;$B$28)&amp;IF($B$29="","",CHAR(10)&amp;"· "&amp;$B$29)&amp;IF($B$30="","",CHAR(10)&amp;"· "&amp;$B$30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="70" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="B56" s="10">
+        <f>"· "&amp;$B$28&amp;IF($B$29="","",CHAR(10)&amp;"· "&amp;$B$29)&amp;IF($B$30="","",CHAR(10)&amp;"· "&amp;$B$30)&amp;IF($B$31="","",CHAR(10)&amp;"· "&amp;$B$31)&amp;IF($B$32="","",CHAR(10)&amp;"· "&amp;$B$32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" ht="70" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>features_list_support</t>
         </is>
       </c>
-      <c r="B55" s="10">
-        <f>$B$54&amp;IF(OR($B$20="",$B$52),"",CHAR(10)&amp;"· Released in support of "&amp;$B$20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>making_ours</t>
-        </is>
-      </c>
-      <c r="B56" s="10">
-        <f>SUBSTITUTE($B$36,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>making_ours_tagged</t>
-        </is>
-      </c>
       <c r="B57" s="10">
-        <f>SUBSTITUTE($B$36,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
+        <f>$B$56&amp;IF(OR($B$22="",$B$54),"",CHAR(10)&amp;"· Released in support of "&amp;$B$22)</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>launch_date</t>
+          <t>making_ours</t>
         </is>
       </c>
       <c r="B58" s="10">
-        <f>TEXT($B$18,"d mmmm")</f>
+        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready")</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>launch_time</t>
+          <t>making_ours_tagged</t>
         </is>
       </c>
       <c r="B59" s="10">
-        <f>TEXT($B$18,"hh:mm")&amp;" UK time"</f>
+        <f>SUBSTITUTE($B$38,"printmakers at Make-Ready","our printmakers at Make-Ready (@make__ready)")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>launch_weekday</t>
+          <t>launch_date</t>
         </is>
       </c>
       <c r="B60" s="10">
-        <f>TEXT($B$18,"dddd")</f>
+        <f>TEXT($B$20,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>launch_date_dd</t>
+          <t>launch_time</t>
         </is>
       </c>
       <c r="B61" s="10">
-        <f>TEXT($B$18,"dd mmmm")</f>
+        <f>TEXT($B$20,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>close_date</t>
+          <t>launch_weekday</t>
         </is>
       </c>
       <c r="B62" s="10">
-        <f>TEXT($B$19,"d mmmm")</f>
+        <f>TEXT($B$20,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>close_time</t>
+          <t>launch_date_dd</t>
         </is>
       </c>
       <c r="B63" s="10">
-        <f>TEXT($B$19,"hh:mm")&amp;" UK time"</f>
+        <f>TEXT($B$20,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>close_weekday</t>
+          <t>close_date</t>
         </is>
       </c>
       <c r="B64" s="10">
-        <f>TEXT($B$19,"dddd")</f>
+        <f>TEXT($B$21,"d mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>close_date_dd</t>
+          <t>close_time</t>
         </is>
       </c>
       <c r="B65" s="10">
-        <f>TEXT($B$19,"dd mmmm")</f>
+        <f>TEXT($B$21,"hh:mm")&amp;" UK time"</f>
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>collect_phrase</t>
+          <t>close_weekday</t>
         </is>
       </c>
       <c r="B66" s="10">
-        <f>SUBSTITUTE($B$13," new "," ",1)</f>
+        <f>TEXT($B$21,"dddd")</f>
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>edition_phrase_cap</t>
+          <t>close_date_dd</t>
         </is>
       </c>
       <c r="B67" s="10">
-        <f>UPPER(LEFT($B$13,1))&amp;MID($B$13,2,999)</f>
+        <f>TEXT($B$21,"dd mmmm")</f>
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>window_cap</t>
+          <t>collect_phrase</t>
         </is>
       </c>
       <c r="B68" s="10">
-        <f>UPPER(LEFT($B$17,1))&amp;MID($B$17,2,999)</f>
+        <f>SUBSTITUTE($B$15," new "," ",1)</f>
         <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>card_line</t>
+          <t>edition_phrase_cap</t>
         </is>
       </c>
       <c r="B69" s="10">
-        <f>$B$67&amp;" by "&amp;$B$4&amp;"."</f>
+        <f>UPPER(LEFT($B$15,1))&amp;MID($B$15,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>card</t>
+          <t>window_cap</t>
         </is>
       </c>
       <c r="B70" s="10">
-        <f>IF($B$12="yes","Untitled",$B$11)&amp;CHAR(10)&amp;$B$69</f>
+        <f>UPPER(LEFT($B$19,1))&amp;MID($B$19,2,999)</f>
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>quote_line</t>
+          <t>card_line</t>
         </is>
       </c>
       <c r="B71" s="10">
-        <f>IF($B$37="","","“"&amp;$B$37&amp;"” – "&amp;$B$4)</f>
+        <f>IF($B$12="",$B$69,"A limited edition "&amp;$B$17)&amp;" by "&amp;$B$4&amp;"."</f>
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>each_artwork</t>
+          <t>card</t>
         </is>
       </c>
       <c r="B72" s="10">
-        <f>IF($B$14&gt;1," for each artwork","")</f>
+        <f>IF($B$14="yes","Untitled",$B$11)&amp;CHAR(10)&amp;$B$71&amp;IF($B$12="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$12&amp;CHAR(10)&amp;$B$71)&amp;IF($B$13="","",CHAR(10)&amp;CHAR(10)&amp;"Card: "&amp;$B$13&amp;CHAR(10)&amp;$B$71)</f>
         <v/>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>work_word</t>
+          <t>quote_line</t>
         </is>
       </c>
       <c r="B73" s="10">
-        <f>IF($B$14&gt;1,"works","work")</f>
+        <f>IF($B$39="","","“"&amp;$B$39&amp;"” – "&amp;$B$4)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
+          <t>each_artwork</t>
+        </is>
+      </c>
+      <c r="B74" s="10">
+        <f>IF($B$16&gt;1," for each artwork","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>work_word</t>
+        </is>
+      </c>
+      <c r="B75" s="10">
+        <f>IF($B$16&gt;1,"works","work")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
           <t>add_what</t>
         </is>
       </c>
-      <c r="B74" s="10">
-        <f>IF($B$14&gt;1,$B$43,$B$46)</f>
+      <c r="B76" s="10">
+        <f>IF($B$16&gt;1,$B$45,$B$48)</f>
         <v/>
       </c>
     </row>
@@ -1519,7 +1545,7 @@
         </is>
       </c>
       <c r="C6" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1535,7 +1561,7 @@
         </is>
       </c>
       <c r="C7" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1551,7 +1577,7 @@
         </is>
       </c>
       <c r="C8" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1567,7 +1593,7 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$37)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B9,"{artist}",Inputs!$B$4),"{quote}",Inputs!$B$39)</f>
         <v/>
       </c>
     </row>
@@ -1583,7 +1609,7 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$40),"{Work}",Inputs!$B$45),"{edition_phrase}",Inputs!$B$13)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B10,"{named}",Inputs!$B$42),"{Work}",Inputs!$B$47),"{edition_phrase}",Inputs!$B$15)</f>
         <v/>
       </c>
     </row>
@@ -1599,7 +1625,7 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$40),"{Work}",Inputs!$B$45),"{window}",Inputs!$B$17)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B11,"{named}",Inputs!$B$42),"{Work}",Inputs!$B$47),"{window}",Inputs!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -1615,7 +1641,7 @@
         </is>
       </c>
       <c r="C12" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B12,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46)</f>
         <v/>
       </c>
     </row>
@@ -1631,7 +1657,7 @@
         </is>
       </c>
       <c r="C13" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B13,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46)</f>
         <v/>
       </c>
     </row>
@@ -1647,7 +1673,7 @@
         </is>
       </c>
       <c r="C14" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$40),"{work}",Inputs!$B$44)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B14,"{named}",Inputs!$B$42),"{work}",Inputs!$B$46)</f>
         <v/>
       </c>
     </row>
@@ -1663,7 +1689,7 @@
         </is>
       </c>
       <c r="C15" s="10">
-        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$53)</f>
+        <f>SUBSTITUTE(B15,"{features}",Inputs!$B$55)</f>
         <v/>
       </c>
     </row>
@@ -1679,7 +1705,7 @@
         </is>
       </c>
       <c r="C16" s="10">
-        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$50)</f>
+        <f>SUBSTITUTE(B16,"{beneficiary_tagged}",Inputs!$B$52)</f>
         <v/>
       </c>
     </row>
@@ -1695,7 +1721,7 @@
         </is>
       </c>
       <c r="C17" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$17),"{launch_date}",Inputs!$B$58),"{launch_time}",Inputs!$B$59)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B17,"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$60),"{launch_time}",Inputs!$B$61)</f>
         <v/>
       </c>
     </row>
@@ -1711,7 +1737,7 @@
         </is>
       </c>
       <c r="C18" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B18,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -1727,7 +1753,7 @@
         </is>
       </c>
       <c r="C19" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$43),"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B19,"{a_unit}",Inputs!$B$45),"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -1743,7 +1769,7 @@
         </is>
       </c>
       <c r="C20" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B20,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -1798,7 +1824,7 @@
         </is>
       </c>
       <c r="C24" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$42),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B24,"{collab_x}",Inputs!$B$44),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -1830,7 +1856,7 @@
         </is>
       </c>
       <c r="C26" s="10">
-        <f>SUBSTITUTE(B26,"{beneficiary}",Inputs!$B$20)</f>
+        <f>SUBSTITUTE(B26,"{beneficiary}",Inputs!$B$22)</f>
         <v/>
       </c>
     </row>
@@ -1846,7 +1872,7 @@
         </is>
       </c>
       <c r="C27" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{link}",Inputs!$B$8),"{window}",Inputs!$B$17),"{launch_date}",Inputs!$B$58),"{launch_time}",Inputs!$B$59)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B27,"{link}",Inputs!$B$8),"{window}",Inputs!$B$19),"{launch_date}",Inputs!$B$60),"{launch_time}",Inputs!$B$61)</f>
         <v/>
       </c>
     </row>
@@ -1862,7 +1888,7 @@
         </is>
       </c>
       <c r="C28" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B28,"{link}",Inputs!$B$8),"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -1878,7 +1904,7 @@
         </is>
       </c>
       <c r="C29" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$43),"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B29,"{link}",Inputs!$B$8),"{a_unit}",Inputs!$B$45),"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -1933,7 +1959,7 @@
         </is>
       </c>
       <c r="C33" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B33,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B33,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -1965,7 +1991,7 @@
         </is>
       </c>
       <c r="C35" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B35,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$43)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B35,"{artist}",Inputs!$B$4),"{a_unit}",Inputs!$B$45)</f>
         <v/>
       </c>
     </row>
@@ -1981,7 +2007,7 @@
         </is>
       </c>
       <c r="C36" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B36,"{framing_code}",Inputs!$B$24),"{framing_percent}",Inputs!$B$25)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B36,"{framing_code}",Inputs!$B$26),"{framing_percent}",Inputs!$B$27)</f>
         <v/>
       </c>
     </row>
@@ -1997,7 +2023,7 @@
         </is>
       </c>
       <c r="C37" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B37,"{framing_code}",Inputs!$B$24),"{framing_percent}",Inputs!$B$25)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B37,"{framing_code}",Inputs!$B$26),"{framing_percent}",Inputs!$B$27)</f>
         <v/>
       </c>
     </row>
@@ -2020,7 +2046,7 @@
         </is>
       </c>
       <c r="C39" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B39,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$67)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B39,"{artist}",Inputs!$B$4),"{edition_phrase_cap}",Inputs!$B$69)</f>
         <v/>
       </c>
     </row>
@@ -2036,7 +2062,7 @@
         </is>
       </c>
       <c r="C40" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2052,7 +2078,7 @@
         </is>
       </c>
       <c r="C41" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59),"{launch_weekday}",Inputs!$B$60),"{launch_date_dd}",Inputs!$B$61)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61),"{launch_weekday}",Inputs!$B$62),"{launch_date_dd}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -2162,7 +2188,7 @@
         </is>
       </c>
       <c r="C49" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B49,"{collab_with}",Inputs!$B$5),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61)</f>
         <v/>
       </c>
     </row>
@@ -2226,7 +2252,7 @@
         </is>
       </c>
       <c r="C53" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2242,7 +2268,7 @@
         </is>
       </c>
       <c r="C54" s="10">
-        <f>SUBSTITUTE(B54,"{launch_date}",Inputs!$B$58)</f>
+        <f>SUBSTITUTE(B54,"{launch_date}",Inputs!$B$60)</f>
         <v/>
       </c>
     </row>
@@ -2258,7 +2284,7 @@
         </is>
       </c>
       <c r="C55" s="10">
-        <f>SUBSTITUTE(B55,"{early_access_code}",Inputs!$B$23)</f>
+        <f>SUBSTITUTE(B55,"{early_access_code}",Inputs!$B$25)</f>
         <v/>
       </c>
     </row>
@@ -2274,7 +2300,7 @@
         </is>
       </c>
       <c r="C56" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10)</f>
         <v/>
       </c>
     </row>
@@ -2290,7 +2316,7 @@
         </is>
       </c>
       <c r="C57" s="10">
-        <f>SUBSTITUTE(B57,"{launch_date}",Inputs!$B$58)</f>
+        <f>SUBSTITUTE(B57,"{launch_date}",Inputs!$B$60)</f>
         <v/>
       </c>
     </row>
@@ -2306,7 +2332,7 @@
         </is>
       </c>
       <c r="C58" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B58,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B58,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61)</f>
         <v/>
       </c>
     </row>
@@ -2322,7 +2348,7 @@
         </is>
       </c>
       <c r="C59" s="10">
-        <f>SUBSTITUTE(B59,"{early_access_code}",Inputs!$B$23)</f>
+        <f>SUBSTITUTE(B59,"{early_access_code}",Inputs!$B$25)</f>
         <v/>
       </c>
     </row>
@@ -2356,7 +2382,7 @@
         </is>
       </c>
       <c r="C61" s="10">
-        <f>SUBSTITUTE(B61,"{advisor}",Inputs!$B$22)</f>
+        <f>SUBSTITUTE(B61,"{advisor}",Inputs!$B$24)</f>
         <v/>
       </c>
     </row>
@@ -2379,7 +2405,7 @@
         </is>
       </c>
       <c r="C63" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B63,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$17)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B63,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51),"{ordinal}",Inputs!$B$10),"{window}",Inputs!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -2395,7 +2421,7 @@
         </is>
       </c>
       <c r="C64" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65),"{add_what}",Inputs!$B$74)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B64,"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67),"{add_what}",Inputs!$B$76)</f>
         <v/>
       </c>
     </row>
@@ -2427,7 +2453,7 @@
         </is>
       </c>
       <c r="C66" s="10">
-        <f>SUBSTITUTE(B66,"{a_unit}",Inputs!$B$43)</f>
+        <f>SUBSTITUTE(B66,"{a_unit}",Inputs!$B$45)</f>
         <v/>
       </c>
     </row>
@@ -2475,7 +2501,7 @@
         </is>
       </c>
       <c r="C69" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$66)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B69,"{artist}",Inputs!$B$4),"{collect_phrase}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -2491,7 +2517,7 @@
         </is>
       </c>
       <c r="C70" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B70,"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -2507,7 +2533,7 @@
         </is>
       </c>
       <c r="C71" s="10">
-        <f>SUBSTITUTE(B71,"{a_unit}",Inputs!$B$43)</f>
+        <f>SUBSTITUTE(B71,"{a_unit}",Inputs!$B$45)</f>
         <v/>
       </c>
     </row>
@@ -2530,7 +2556,7 @@
         </is>
       </c>
       <c r="C73" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$66),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B73,"{collab_with}",Inputs!$B$5),"{collect_phrase}",Inputs!$B$68),"{ordinal}",Inputs!$B$10),"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -2546,7 +2572,7 @@
         </is>
       </c>
       <c r="C74" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B74,"{each_artwork}",Inputs!$B$72),"{work_word}",Inputs!$B$73)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B74,"{each_artwork}",Inputs!$B$74),"{work_word}",Inputs!$B$75)</f>
         <v/>
       </c>
     </row>
@@ -2562,7 +2588,7 @@
         </is>
       </c>
       <c r="C75" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$46),"{collect_phrase}",Inputs!$B$66)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75,"{artist}",Inputs!$B$4),"{work_email}",Inputs!$B$48),"{collect_phrase}",Inputs!$B$68)</f>
         <v/>
       </c>
     </row>
@@ -2578,7 +2604,7 @@
         </is>
       </c>
       <c r="C76" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{close_time}",Inputs!$B$63),"{close_weekday}",Inputs!$B$64),"{close_date_dd}",Inputs!$B$65)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76,"{close_time}",Inputs!$B$65),"{close_weekday}",Inputs!$B$66),"{close_date_dd}",Inputs!$B$67)</f>
         <v/>
       </c>
     </row>
@@ -2633,7 +2659,7 @@
         </is>
       </c>
       <c r="C80" s="10">
-        <f>SUBSTITUTE(B80,"{advisor}",Inputs!$B$22)</f>
+        <f>SUBSTITUTE(B80,"{advisor}",Inputs!$B$24)</f>
         <v/>
       </c>
     </row>
@@ -2768,7 +2794,7 @@
         </is>
       </c>
       <c r="C89" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$48),"{support}",Inputs!$B$49)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B89,"{collab_with}",Inputs!$B$5),"{work_intro}",Inputs!$B$50),"{support}",Inputs!$B$51)</f>
         <v/>
       </c>
     </row>
@@ -2784,7 +2810,7 @@
         </is>
       </c>
       <c r="C90" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(B90,"{close_date}",Inputs!$B$62),"{close_time}",Inputs!$B$63)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(B90,"{close_date}",Inputs!$B$64),"{close_time}",Inputs!$B$65)</f>
         <v/>
       </c>
     </row>
@@ -2800,7 +2826,7 @@
         </is>
       </c>
       <c r="C91" s="10">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91,"{window}",Inputs!$B$17),"{launch_time}",Inputs!$B$59),"{launch_weekday}",Inputs!$B$60),"{launch_date_dd}",Inputs!$B$61)</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91,"{window}",Inputs!$B$19),"{launch_time}",Inputs!$B$61),"{launch_weekday}",Inputs!$B$62),"{launch_date_dd}",Inputs!$B$63)</f>
         <v/>
       </c>
     </row>
@@ -2926,7 +2952,7 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>Inputs!$B$51</f>
+        <f>Inputs!$B$53</f>
         <v/>
       </c>
       <c r="G4" s="11">
@@ -2970,19 +2996,19 @@
         </is>
       </c>
       <c r="E5" s="11">
-        <f>IF(Inputs!$B$12="yes",Lines!$C$7,Lines!$C$6)</f>
+        <f>IF(Inputs!$B$14="yes",Lines!$C$7,Lines!$C$6)</f>
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$36</f>
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$52,"",IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$54,"",IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H5" s="11">
-        <f>IF(Inputs!$B$16="draw",Lines!$C$18,Lines!$C$17)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$18,Lines!$C$17)</f>
         <v/>
       </c>
       <c r="I5" s="11">
@@ -3022,15 +3048,15 @@
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>Inputs!$B$57</f>
+        <f>Inputs!$B$59</f>
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H6" s="11">
-        <f>IF(Inputs!$B$16="draw",Lines!$C$18,Lines!$C$17)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$18,Lines!$C$17)</f>
         <v/>
       </c>
       <c r="I6" s="11">
@@ -3066,19 +3092,19 @@
         </is>
       </c>
       <c r="E7" s="11">
-        <f>IF(Inputs!$B$37="","(no quote given, post skipped)",Lines!$C$9)</f>
+        <f>IF(Inputs!$B$39="","(no quote given, post skipped)",Lines!$C$9)</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>IF(Inputs!$B$37="","",Lines!$C$10)</f>
+        <f>IF(Inputs!$B$39="","",Lines!$C$10)</f>
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>IF(Inputs!$B$37="","",Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$39="","",Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H7" s="11">
-        <f>IF(Inputs!$B$37="","",IF(Inputs!$B$16="draw",Lines!$C$18,Lines!$C$17))</f>
+        <f>IF(Inputs!$B$39="","",IF(Inputs!$B$18="draw",Lines!$C$18,Lines!$C$17))</f>
         <v/>
       </c>
       <c r="I7" s="11">
@@ -3086,7 +3112,7 @@
         <v/>
       </c>
       <c r="J7" s="11">
-        <f>IF(Inputs!$B$37="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
+        <f>IF(Inputs!$B$39="","(no quote given, post skipped)",E7&amp;IF(F7="","",CHAR(10)&amp;CHAR(10)&amp;F7)&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7)&amp;IF(H7="","",CHAR(10)&amp;CHAR(10)&amp;H7))</f>
         <v/>
       </c>
       <c r="K7" s="11">
@@ -3114,7 +3140,7 @@
         </is>
       </c>
       <c r="E8" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",Lines!$C$11)</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",Lines!$C$11)</f>
         <v/>
       </c>
       <c r="F8" s="11">
@@ -3122,11 +3148,11 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IF(Inputs!$B$16="draw","",Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H8" s="11">
-        <f>IF(Inputs!$B$16="draw","",IF(Inputs!$B$16="draw",Lines!$C$20,Lines!$C$19))</f>
+        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$20,Lines!$C$19))</f>
         <v/>
       </c>
       <c r="I8" s="11">
@@ -3134,7 +3160,7 @@
         <v/>
       </c>
       <c r="J8" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",E8&amp;IF(G8="","",CHAR(10)&amp;CHAR(10)&amp;G8)&amp;IF(H8="","",CHAR(10)&amp;CHAR(10)&amp;H8))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",E8&amp;IF(G8="","",CHAR(10)&amp;CHAR(10)&amp;G8)&amp;IF(H8="","",CHAR(10)&amp;CHAR(10)&amp;H8))</f>
         <v/>
       </c>
       <c r="K8" s="11">
@@ -3162,7 +3188,7 @@
         </is>
       </c>
       <c r="E9" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",Lines!$C$12)</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",Lines!$C$12)</f>
         <v/>
       </c>
       <c r="F9" s="11">
@@ -3170,11 +3196,11 @@
         <v/>
       </c>
       <c r="G9" s="11">
-        <f>IF(Inputs!$B$16="draw","",Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16))</f>
+        <f>IF(Inputs!$B$18="draw","",Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16))</f>
         <v/>
       </c>
       <c r="H9" s="11">
-        <f>IF(Inputs!$B$16="draw","",IF(Inputs!$B$16="draw",Lines!$C$20,Lines!$C$19))</f>
+        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$20,Lines!$C$19))</f>
         <v/>
       </c>
       <c r="I9" s="11">
@@ -3182,7 +3208,7 @@
         <v/>
       </c>
       <c r="J9" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",E9&amp;IF(G9="","",CHAR(10)&amp;CHAR(10)&amp;G9)&amp;IF(H9="","",CHAR(10)&amp;CHAR(10)&amp;H9))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",E9&amp;IF(G9="","",CHAR(10)&amp;CHAR(10)&amp;G9)&amp;IF(H9="","",CHAR(10)&amp;CHAR(10)&amp;H9))</f>
         <v/>
       </c>
       <c r="K9" s="11">
@@ -3210,7 +3236,7 @@
         </is>
       </c>
       <c r="E10" s="11">
-        <f>IF(Inputs!$B$16="draw",Lines!$C$14,Lines!$C$13)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$14,Lines!$C$13)</f>
         <v/>
       </c>
       <c r="F10" s="11">
@@ -3218,11 +3244,11 @@
         <v/>
       </c>
       <c r="G10" s="11">
-        <f>Lines!$C$15&amp;IF(Inputs!$B$50="",""," "&amp;Lines!$C$16)</f>
+        <f>Lines!$C$15&amp;IF(Inputs!$B$52="",""," "&amp;Lines!$C$16)</f>
         <v/>
       </c>
       <c r="H10" s="11">
-        <f>IF(Inputs!$B$16="draw",Lines!$C$20,Lines!$C$19)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$20,Lines!$C$19)</f>
         <v/>
       </c>
       <c r="I10" s="11">
@@ -3378,19 +3404,19 @@
         </is>
       </c>
       <c r="D5" s="11">
-        <f>SUBSTITUTE(IF(Inputs!$B$12="yes",Lines!$C$7,Lines!$C$6),Inputs!$B$40,Inputs!$B$41)</f>
+        <f>SUBSTITUTE(IF(Inputs!$B$14="yes",Lines!$C$7,Lines!$C$6),Inputs!$B$42,Inputs!$B$43)</f>
         <v/>
       </c>
       <c r="E5" s="11">
-        <f>Inputs!$B$34</f>
+        <f>Inputs!$B$36</f>
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>IF(OR(Inputs!$B$20="",Inputs!$B$52),"",Lines!$C$26)</f>
+        <f>IF(OR(Inputs!$B$22="",Inputs!$B$54),"",Lines!$C$26)</f>
         <v/>
       </c>
       <c r="G5" s="11">
-        <f>IF(Inputs!$B$16="draw",Lines!$C$28,Lines!$C$27)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$27)</f>
         <v/>
       </c>
       <c r="H5" s="11">
@@ -3417,7 +3443,7 @@
         </is>
       </c>
       <c r="D6" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$40,Inputs!$B$41))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$11,Inputs!$B$42,Inputs!$B$43))</f>
         <v/>
       </c>
       <c r="E6" s="11">
@@ -3429,11 +3455,11 @@
         <v/>
       </c>
       <c r="G6" s="11">
-        <f>IF(Inputs!$B$16="draw","",IF(Inputs!$B$16="draw",Lines!$C$28,Lines!$C$29))</f>
+        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$29))</f>
         <v/>
       </c>
       <c r="H6" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",D6&amp;IF(G6="","",CHAR(10)&amp;CHAR(10)&amp;G6))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",D6&amp;IF(G6="","",CHAR(10)&amp;CHAR(10)&amp;G6))</f>
         <v/>
       </c>
       <c r="I6" s="11">
@@ -3456,7 +3482,7 @@
         </is>
       </c>
       <c r="D7" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$40,Inputs!$B$41))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",SUBSTITUTE(Lines!$C$12,Inputs!$B$42,Inputs!$B$43))</f>
         <v/>
       </c>
       <c r="E7" s="11">
@@ -3468,11 +3494,11 @@
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>IF(Inputs!$B$16="draw","",IF(Inputs!$B$16="draw",Lines!$C$28,Lines!$C$29))</f>
+        <f>IF(Inputs!$B$18="draw","",IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$29))</f>
         <v/>
       </c>
       <c r="H7" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",D7&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",D7&amp;IF(G7="","",CHAR(10)&amp;CHAR(10)&amp;G7))</f>
         <v/>
       </c>
       <c r="I7" s="11">
@@ -3495,7 +3521,7 @@
         </is>
       </c>
       <c r="D8" s="11">
-        <f>IF(Inputs!$B$16="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$40,Inputs!$B$41),SUBSTITUTE(Lines!$C$13,Inputs!$B$40,Inputs!$B$41))</f>
+        <f>IF(Inputs!$B$18="draw",SUBSTITUTE(Lines!$C$14,Inputs!$B$42,Inputs!$B$43),SUBSTITUTE(Lines!$C$13,Inputs!$B$42,Inputs!$B$43))</f>
         <v/>
       </c>
       <c r="E8" s="11">
@@ -3507,7 +3533,7 @@
         <v/>
       </c>
       <c r="G8" s="11">
-        <f>IF(Inputs!$B$16="draw",Lines!$C$28,Lines!$C$29)</f>
+        <f>IF(Inputs!$B$18="draw",Lines!$C$28,Lines!$C$29)</f>
         <v/>
       </c>
       <c r="H8" s="11">
@@ -3664,35 +3690,35 @@
         <v/>
       </c>
       <c r="F4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$62&amp;".","Launching "&amp;Inputs!$B$58&amp;". Register for updates."))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw for a chance to collect. Closes "&amp;Inputs!$B$64&amp;".","Launching "&amp;Inputs!$B$60&amp;". Register for updates."))</f>
         <v/>
       </c>
       <c r="G4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw","Launching "&amp;Inputs!$B$58))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Launching "&amp;Inputs!$B$60))</f>
         <v/>
       </c>
       <c r="H4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw",Inputs!$B$47,Inputs!$B$47&amp;" by "&amp;Inputs!$B$4))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw",Inputs!$B$49,Inputs!$B$49&amp;" by "&amp;Inputs!$B$4))</f>
         <v/>
       </c>
       <c r="I4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$40&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(Inputs!$B$54="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$54)&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42))))))</f>
+        <f>IF($D4&lt;&gt;"yes","",(Lines!$C$40&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$58="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$58)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42)))="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$33,(Lines!$C$41&amp;IF(Lines!$C$42="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$42))))))</f>
         <v/>
       </c>
       <c r="J4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw","Discover the collaboration"))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Discover the collaboration"))</f>
         <v/>
       </c>
       <c r="K4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="L4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$71)</f>
+        <f>IF($D4&lt;&gt;"yes","",Inputs!$B$73)</f>
         <v/>
       </c>
       <c r="M4" s="11">
-        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Collect "&amp;Inputs!$B$66,"Launching "&amp;Inputs!$B$58))</f>
+        <f>IF($D4&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Collect "&amp;Inputs!$B$68,"Launching "&amp;Inputs!$B$60))</f>
         <v/>
       </c>
       <c r="N4" s="11">
@@ -3719,7 +3745,7 @@
         </is>
       </c>
       <c r="D5" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)","yes")</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)","yes")</f>
         <v/>
       </c>
       <c r="E5" s="11">
@@ -3782,7 +3808,7 @@
         </is>
       </c>
       <c r="D6" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)","yes")</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)","yes")</f>
         <v/>
       </c>
       <c r="E6" s="11">
@@ -3802,7 +3828,7 @@
         <v/>
       </c>
       <c r="I6" s="11">
-        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$36))&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)))</f>
+        <f>IF($D6&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$57="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$57)&amp;IF(Lines!$C$50="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$50)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)))</f>
         <v/>
       </c>
       <c r="J6" s="11">
@@ -3845,7 +3871,7 @@
         </is>
       </c>
       <c r="D7" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)","yes")</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)","yes")</f>
         <v/>
       </c>
       <c r="E7" s="11">
@@ -3865,7 +3891,7 @@
         <v/>
       </c>
       <c r="I7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
+        <f>IF($D7&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$49="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$49)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$57="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$57)&amp;IF(Lines!$C$51="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$51)&amp;IF(Lines!$C$52="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$52)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
         <v/>
       </c>
       <c r="J7" s="11">
@@ -3873,7 +3899,7 @@
         <v/>
       </c>
       <c r="K7" s="11">
-        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D7&lt;&gt;"yes","",Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="L7" s="11">
@@ -3916,7 +3942,7 @@
         <v/>
       </c>
       <c r="F8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",IF(Inputs!$B$16="draw","A first look, plus early access to a limited number of pre-orders.","Collect 24 hours before everyone else."))</f>
+        <f>IF($D8&lt;&gt;"yes","",IF(Inputs!$B$18="draw","A first look, plus early access to a limited number of pre-orders.","Collect 24 hours before everyone else."))</f>
         <v/>
       </c>
       <c r="G8" s="11">
@@ -3928,7 +3954,7 @@
         <v/>
       </c>
       <c r="I8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$56="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$56)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$57,Lines!$C$58)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$57,Lines!$C$58))&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$59,Lines!$C$60)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$59,Lines!$C$60))&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)&amp;IF(Lines!$C$61="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$61)))</f>
+        <f>IF($D8&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$56="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$56)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$57,Lines!$C$58)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$57,Lines!$C$58))&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$59,Lines!$C$60)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$59,Lines!$C$60))&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)&amp;IF(Lines!$C$61="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$61)))</f>
         <v/>
       </c>
       <c r="J8" s="11">
@@ -3936,7 +3962,7 @@
         <v/>
       </c>
       <c r="K8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D8&lt;&gt;"yes","",Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="L8" s="11">
@@ -3944,7 +3970,7 @@
         <v/>
       </c>
       <c r="M8" s="11">
-        <f>IF($D8&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Especially for you.","24 hours ahead of the public launch"))</f>
+        <f>IF($D8&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Especially for you.","24 hours ahead of the public launch"))</f>
         <v/>
       </c>
       <c r="N8" s="11">
@@ -3971,7 +3997,7 @@
         </is>
       </c>
       <c r="D9" s="11">
-        <f>IF(Inputs!$B$16="draw","yes","(not used for a timed edition)")</f>
+        <f>IF(Inputs!$B$18="draw","yes","(not used for a timed edition)")</f>
         <v/>
       </c>
       <c r="E9" s="11">
@@ -3991,7 +4017,7 @@
         <v/>
       </c>
       <c r="I9" s="11">
-        <f>IF($D9&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Lines!$C$54="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$54)&amp;IF(Lines!$C$55="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$55)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
+        <f>IF($D9&lt;&gt;"yes","",(Lines!$C$31&amp;IF(Lines!$C$53="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$53)&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$54="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$54)&amp;IF(Lines!$C$55="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$55)&amp;IF(Lines!$C$34="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$34)&amp;IF(Lines!$C$32="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$32)))</f>
         <v/>
       </c>
       <c r="J9" s="11">
@@ -3999,7 +4025,7 @@
         <v/>
       </c>
       <c r="K9" s="11">
-        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D9&lt;&gt;"yes","",Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="L9" s="11">
@@ -4034,15 +4060,15 @@
         </is>
       </c>
       <c r="D10" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)","yes")</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)","yes")</f>
         <v/>
       </c>
       <c r="E10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$4&amp;" – Available now, for "&amp;Inputs!$B$17&amp;" only")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$4&amp;" – Available now, for "&amp;Inputs!$B$19&amp;" only")</f>
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$68&amp;", starting now.")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$70&amp;", starting now.")</f>
         <v/>
       </c>
       <c r="G10" s="11">
@@ -4050,11 +4076,11 @@
         <v/>
       </c>
       <c r="H10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$68&amp;", starting now")</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$70&amp;", starting now")</f>
         <v/>
       </c>
       <c r="I10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$63&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(Inputs!$B$55="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$55)&amp;IF(Lines!$C$64="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$64)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$36))))</f>
+        <f>IF($D10&lt;&gt;"yes","",(Lines!$C$63&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$58="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$58)&amp;IF(Inputs!$B$57="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$57)&amp;IF(Lines!$C$64="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$64)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$36)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$36))))</f>
         <v/>
       </c>
       <c r="J10" s="11">
@@ -4062,15 +4088,15 @@
         <v/>
       </c>
       <c r="K10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="L10" s="11">
-        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$71)</f>
+        <f>IF($D10&lt;&gt;"yes","",Inputs!$B$73)</f>
         <v/>
       </c>
       <c r="M10" s="11">
-        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$66)</f>
+        <f>IF($D10&lt;&gt;"yes","","Collect "&amp;Inputs!$B$68)</f>
         <v/>
       </c>
       <c r="N10" s="11">
@@ -4097,7 +4123,7 @@
         </is>
       </c>
       <c r="D11" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",IF(Inputs!$B$17="48 hours","yes","(48-hour windows only; a one-week window gets the 5 days and 3 days emails)"))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",IF(Inputs!$B$19="48 hours","yes","(48-hour windows only; a one-week window gets the 5 days and 3 days emails)"))</f>
         <v/>
       </c>
       <c r="E11" s="11">
@@ -4160,7 +4186,7 @@
         </is>
       </c>
       <c r="D12" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",IF(Inputs!$B$17="48 hours","(one-week windows only; a 48-hour window gets the halfway email)","yes"))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",IF(Inputs!$B$19="48 hours","(one-week windows only; a 48-hour window gets the halfway email)","yes"))</f>
         <v/>
       </c>
       <c r="E12" s="11">
@@ -4184,7 +4210,7 @@
         <v/>
       </c>
       <c r="J12" s="11">
-        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$43)</f>
+        <f>IF($D12&lt;&gt;"yes","","Buy "&amp;Inputs!$B$45)</f>
         <v/>
       </c>
       <c r="K12" s="11">
@@ -4223,7 +4249,7 @@
         </is>
       </c>
       <c r="D13" s="11">
-        <f>IF(Inputs!$B$16="draw","(not used for a draw)",IF(Inputs!$B$17="48 hours","(one-week windows only; a 48-hour window gets the halfway email)","yes"))</f>
+        <f>IF(Inputs!$B$18="draw","(not used for a draw)",IF(Inputs!$B$19="48 hours","(one-week windows only; a 48-hour window gets the halfway email)","yes"))</f>
         <v/>
       </c>
       <c r="E13" s="11">
@@ -4235,7 +4261,7 @@
         <v/>
       </c>
       <c r="G13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$47&amp;" by "&amp;Inputs!$B$4)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$49&amp;" by "&amp;Inputs!$B$4)</f>
         <v/>
       </c>
       <c r="H13" s="11">
@@ -4243,15 +4269,15 @@
         <v/>
       </c>
       <c r="I13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",(Lines!$C$69&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Lines!$C$70="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$70)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$37))))</f>
+        <f>IF($D13&lt;&gt;"yes","",(Lines!$C$69&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$70="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$70)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37))))</f>
         <v/>
       </c>
       <c r="J13" s="11">
-        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$43)</f>
+        <f>IF($D13&lt;&gt;"yes","","Buy "&amp;Inputs!$B$45)</f>
         <v/>
       </c>
       <c r="K13" s="11">
-        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D13&lt;&gt;"yes","",Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="L13" s="11">
@@ -4290,11 +4316,11 @@
         <v/>
       </c>
       <c r="E14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$4&amp;" – Last chance to "&amp;IF(Inputs!$B$16="draw","enter the draw","collect"))</f>
+        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$4&amp;" – Last chance to "&amp;IF(Inputs!$B$18="draw","enter the draw","collect"))</f>
         <v/>
       </c>
       <c r="F14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$16="draw","The draw closes at "&amp;Inputs!$B$63&amp;" on "&amp;Inputs!$B$62&amp;".","Time is almost up."))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","The draw closes at "&amp;Inputs!$B$65&amp;" on "&amp;Inputs!$B$64&amp;".","Time is almost up."))</f>
         <v/>
       </c>
       <c r="G14" s="11">
@@ -4302,19 +4328,19 @@
         <v/>
       </c>
       <c r="H14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Last chance to enter the draw","Last chance to collect"))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Last chance to enter the draw","Last chance to collect"))</f>
         <v/>
       </c>
       <c r="I14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$16="draw",(Lines!$C$75&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Lines!$C$76="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$76)),(Lines!$C$73&amp;IF(Lines!$C$74="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$74)&amp;IF(IF(Inputs!$B$24="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$24="","",Lines!$C$37)))))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw",(Lines!$C$75&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Lines!$C$76="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$76)),(Lines!$C$73&amp;IF(Lines!$C$74="","",CHAR(10)&amp;CHAR(10)&amp;Lines!$C$74)&amp;IF(IF(Inputs!$B$26="","",Lines!$C$37)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$26="","",Lines!$C$37)))))</f>
         <v/>
       </c>
       <c r="J14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$16="draw","Enter the draw","Buy now"))</f>
+        <f>IF($D14&lt;&gt;"yes","",IF(Inputs!$B$18="draw","Enter the draw","Buy now"))</f>
         <v/>
       </c>
       <c r="K14" s="11">
-        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$70)</f>
+        <f>IF($D14&lt;&gt;"yes","",Inputs!$B$72)</f>
         <v/>
       </c>
       <c r="L14" s="11">
@@ -4349,7 +4375,7 @@
         </is>
       </c>
       <c r="D15" s="11">
-        <f>IF(Inputs!$B$16="draw","yes","(not used for a timed edition)")</f>
+        <f>IF(Inputs!$B$18="draw","yes","(not used for a timed edition)")</f>
         <v/>
       </c>
       <c r="E15" s="11">
@@ -4412,7 +4438,7 @@
         </is>
       </c>
       <c r="D16" s="11">
-        <f>IF(Inputs!$B$16="draw","yes","(not used for a timed edition)")</f>
+        <f>IF(Inputs!$B$18="draw","yes","(not used for a timed edition)")</f>
         <v/>
       </c>
       <c r="E16" s="11">
@@ -4495,7 +4521,7 @@
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$89&amp;IF(Inputs!$B$34="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$34)&amp;IF(Inputs!$B$56="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$56)&amp;IF(IF(Inputs!$B$16="draw",Lines!$C$90,Lines!$C$91)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$16="draw",Lines!$C$90,Lines!$C$91))))</f>
+        <f>IF($D17&lt;&gt;"yes","",(Lines!$C$89&amp;IF(Inputs!$B$36="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$36)&amp;IF(Inputs!$B$58="","",CHAR(10)&amp;CHAR(10)&amp;Inputs!$B$58)&amp;IF(IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91)="","",CHAR(10)&amp;CHAR(10)&amp;IF(Inputs!$B$18="draw",Lines!$C$90,Lines!$C$91))))</f>
         <v/>
       </c>
       <c r="J17" s="11">

--- a/tool/release-copy-lucian-freud-tl-26.xlsx
+++ b/tool/release-copy-lucian-freud-tl-26.xlsx
@@ -979,7 +979,7 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Fragments, written once per release. Voice-neutral: no we or our, no artist name in the hook or making line.</t>
+          <t>Fragments, written once per release. No we or our: the sheet adds our where a line needs it.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>1 to 2 sentences about the work only. Reused in every post and email.</t>
+          <t>2 to 3 sentences about the work. Write it as editorially as you like; the one test is that it must read as well in the middle of an email as at the top of a post. Self-contained, no rhetorical question. It reaches 16 slots, so it is the one fragment that must stand alone.</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4637,142 +4637,154 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Naming the work</t>
+          <t>The hook carries the voice</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>The opener's tail is the title (single print only), the edition phrase, and the qualifier if one is written: 'The Changeling, a new limited edition print'; 'a quartet of new limited edition prints spanning five decades of the artist's career'; 'six new limited edition prints from his iconic Dream House series'. A pair or a quartet takes no title; the hook names the work. The same tail is used by the Insiders email, LE early access, Now Live and the Monthly Preview paragraph.</t>
+          <t>The hook is where a release sounds like itself, and it can be as editorial as the writer likes: 'Folklore says a changeling is a child swapped at birth for something not quite human. Grayson Perry's version is the generation raised by screens, and he means it to disturb.' The one test is that it must read as well in the middle of an email as at the top of a post, because it appears in 16 slots and most of them are middle paragraphs. That rules out a sentence which assumes it is opening: a rhetorical question, or an aside about the artist that never describes the work.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Fragments</t>
+          <t>Naming the work</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Four per release, written once: bio (2 to 3 sentences, Coming Soon only), hook (1 to 2 sentences about the work, in every post and email), making (one sentence on how it was made), quote (verbatim). The hook and bio must not repeat each other.</t>
+          <t>The opener's tail is the title (single print only), the edition phrase, and the qualifier if one is written: 'The Changeling, a new limited edition print'; 'a quartet of new limited edition prints spanning five decades of the artist's career'; 'six new limited edition prints from his iconic Dream House series'. A pair or a quartet takes no title; the hook names the work. The same tail is used by the Insiders email, LE early access, Now Live and the Monthly Preview paragraph.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Voice</t>
+          <t>Fragments</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Fragments are voice-neutral: no we or our, no artist name in the hook or the making line, and 'printmakers at Make-Ready' where it applies. The sheet adds 'our'. The Insiders email and the first-time survey are signed by the advisor named on Inputs. Features never say 'our'.</t>
+          <t>Four per release, written once: bio (2 to 3 sentences, Coming Soon only), hook (2 to 3 sentences about the work, in every post and email), making (one sentence on how it was made), quote (verbatim). The hook and bio must not repeat each other.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Who and what</t>
+          <t>Voice</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>'by {artist}' is always the artist. 'collaboration with {collab_with}' is the artist's name, or the estate. 'unit' is what one is called (print, embroidery, sculpture), and the sheet writes 'a print' or 'an embroidery' wherever a line names one.</t>
+          <t>Fragments never say we or our, and the making line says 'printmakers at Make-Ready' so the sheet can add 'our'. The hook may name the artist. The Insiders email and the first-time survey are signed by the advisor named on Inputs. Features never say 'our'.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Features</t>
+          <t>Who and what</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>The standard three (signed by the artist, individually numbered, free worldwide shipping) plus anything bespoke: framed, a set offer, a partner credit. One line of short sentences in a post, a list in an email. The beneficiary follows, named once.</t>
+          <t>'by {artist}' is always the artist. 'collaboration with {collab_with}' is the artist's name, or the estate. 'unit' is what one is called (print, embroidery, sculpture), and the sheet writes 'a print' or 'an embroidery' wherever a line names one.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Beneficiary</t>
+          <t>Features</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>One phrase everywhere: 'released in support of'. It goes in the opener unless the hook already names the beneficiary.</t>
+          <t>The standard three (signed by the artist, individually numbered, free worldwide shipping) plus anything bespoke: framed, a set offer, a partner credit. One line of short sentences in a post, a list in an email. The beneficiary follows, named once.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Framing offer</t>
+          <t>Beneficiary</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>A framing code on Inputs adds the first-purchase framing line to Early Access, Now Live, 3 days to go and Last chance. Blank means no offer.</t>
+          <t>One phrase everywhere: 'released in support of'. It goes in the opener unless the hook already names the beneficiary.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Action lines</t>
+          <t>Framing offer</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Three CTAs: get updates before launch, enter the draw for a draw, buy one for an open window. One deadline form: Closes {date} at {time} UK time, or 'until {time} on {weekday}, {date}' in an email.</t>
+          <t>A framing code on Inputs adds the first-purchase framing line to Early Access, Now Live, 3 days to go and Last chance. Blank means no offer.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Mechanic and window</t>
+          <t>Action lines</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Set mechanic to timed or draw and the sheet switches every line. For a timed edition, a 48-hour window gets the halfway email; a one-week window gets 5 days to go and 3 days to go.</t>
+          <t>Three CTAs: get updates before launch, enter the draw for a draw, buy one for an open window. One deadline form: Closes {date} at {time} UK time, or 'until {time} on {weekday}, {date}' in an email.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Dates</t>
+          <t>Mechanic and window</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Enter launch and close once as date and time; the sheet derives '30 April', '14:00 UK time', 'Thursday' and '07 May' where each email needs them.</t>
+          <t>Set mechanic to timed or draw and the sheet switches every line. For a timed edition, a 48-hour window gets the halfway email; a one-week window gets 5 days to go and 3 days to go.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>What stays written</t>
+          <t>Dates</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>A delay reason, a framing paragraph, editorial deep dives, the rest of the Monthly Preview, the artist's own email, artist-local times, and anything for a second release.</t>
+          <t>Enter launch and close once as date and time; the sheet derives '30 April', '14:00 UK time', 'Thursday' and '07 May' where each email needs them.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="12" t="inlineStr">
         <is>
+          <t>What stays written</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>A delay reason, a framing paragraph, editorial deep dives, the rest of the Monthly Preview, the artist's own email, artist-local times, and anything for a second release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
           <t>How to use</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Fill the blue cells on Inputs. Read Posts, Tweets and Emails. To change the house wording, edit the blue cells on Lines once.</t>
         </is>
